--- a/data/trans_orig/IP74A5_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP74A5_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto los impuestos.. en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de los impuestos relacionados con vehículos, IBI, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>326</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>88,53%</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>774</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>552</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,73%</t>
         </is>
       </c>
     </row>
